--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1e6ab86d0a4749ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42272c48c54049bd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42272c48c54049bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raaea7e9110e640c8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raaea7e9110e640c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2ab143b491ee4be8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2ab143b491ee4be8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd8b76d2dc7b341f0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd8b76d2dc7b341f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa58b1ef2b7a4f20"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa58b1ef2b7a4f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33776468be744b26"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33776468be744b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd66b58487d5b4fa6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd66b58487d5b4fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7ee2d0adb3ed497d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7ee2d0adb3ed497d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R071f401dae514aa1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R071f401dae514aa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re79c66da36e34177"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re79c66da36e34177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb0a9050600bd4e7b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb0a9050600bd4e7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd94636e7bf0a4841"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd94636e7bf0a4841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc32ab8c986f340e8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc32ab8c986f340e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re688dc17e61d4b6b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re688dc17e61d4b6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c28693405cd4124"/>
   </x:sheets>
 </x:workbook>
 </file>
